--- a/experiment3/test5.xlsx
+++ b/experiment3/test5.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="224">
   <si>
     <t xml:space="preserve">prompt</t>
   </si>
@@ -1031,7 +1031,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1505,8 +1505,8 @@
       <c r="C30" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>15</v>
+      <c r="E30" s="4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
